--- a/artfynd/A 58997-2025 artfynd.xlsx
+++ b/artfynd/A 58997-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -891,7 +891,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130222759</v>
+        <v>130222885</v>
       </c>
       <c r="B4" t="n">
         <v>98833</v>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>557582</v>
+        <v>557566</v>
       </c>
       <c r="R4" t="n">
-        <v>6398323</v>
+        <v>6398326</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -997,7 +997,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130222885</v>
+        <v>130222759</v>
       </c>
       <c r="B5" t="n">
         <v>98833</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>557566</v>
+        <v>557582</v>
       </c>
       <c r="R5" t="n">
-        <v>6398326</v>
+        <v>6398323</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130222200</v>
+        <v>130222398</v>
       </c>
       <c r="B6" t="n">
-        <v>92236</v>
+        <v>98833</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,34 +1114,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1149,13 +1146,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>557636</v>
+        <v>557564</v>
       </c>
       <c r="R6" t="n">
-        <v>6398339</v>
+        <v>6398402</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,42 +1209,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130222398</v>
+        <v>130222889</v>
       </c>
       <c r="B7" t="n">
-        <v>98833</v>
+        <v>92923</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>557564</v>
+        <v>557475</v>
       </c>
       <c r="R7" t="n">
-        <v>6398402</v>
+        <v>6398291</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,32 +1318,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130222889</v>
+        <v>130222761</v>
       </c>
       <c r="B8" t="n">
-        <v>92923</v>
+        <v>91662</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1364,10 +1364,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>557475</v>
+        <v>557576</v>
       </c>
       <c r="R8" t="n">
-        <v>6398291</v>
+        <v>6398344</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,32 +1427,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130222761</v>
+        <v>130222371</v>
       </c>
       <c r="B9" t="n">
-        <v>91662</v>
+        <v>92291</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>1339</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1473,13 +1473,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>557576</v>
+        <v>557559</v>
       </c>
       <c r="R9" t="n">
-        <v>6398344</v>
+        <v>6398440</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1536,45 +1536,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130222371</v>
+        <v>130222698</v>
       </c>
       <c r="B10" t="n">
-        <v>92291</v>
+        <v>98833</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1582,13 +1579,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>557559</v>
+        <v>557563</v>
       </c>
       <c r="R10" t="n">
-        <v>6398440</v>
+        <v>6398331</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1645,42 +1642,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130222698</v>
+        <v>130222194</v>
       </c>
       <c r="B11" t="n">
-        <v>98833</v>
+        <v>92923</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>557563</v>
+        <v>557636</v>
       </c>
       <c r="R11" t="n">
-        <v>6398331</v>
+        <v>6398339</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1751,45 +1751,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130222194</v>
+        <v>130222391</v>
       </c>
       <c r="B12" t="n">
-        <v>92923</v>
+        <v>98833</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1797,10 +1794,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>557636</v>
+        <v>557554</v>
       </c>
       <c r="R12" t="n">
-        <v>6398339</v>
+        <v>6398411</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1860,7 +1857,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130222391</v>
+        <v>130222384</v>
       </c>
       <c r="B13" t="n">
         <v>98833</v>
@@ -1903,10 +1900,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>557554</v>
+        <v>557527</v>
       </c>
       <c r="R13" t="n">
-        <v>6398411</v>
+        <v>6398444</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1966,7 +1963,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130222384</v>
+        <v>130222404</v>
       </c>
       <c r="B14" t="n">
         <v>98833</v>
@@ -2009,10 +2006,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557527</v>
+        <v>557549</v>
       </c>
       <c r="R14" t="n">
-        <v>6398444</v>
+        <v>6398333</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2176,112 +2173,6 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>130222404</v>
-      </c>
-      <c r="B16" t="n">
-        <v>98833</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>A 58997, Gunnebo, Sm</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>557549</v>
-      </c>
-      <c r="R16" t="n">
-        <v>6398333</v>
-      </c>
-      <c r="S16" t="n">
-        <v>10</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Vimmerby</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Frödinge</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2025-12-19</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2025-12-19</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="inlineStr"/>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58997-2025 artfynd.xlsx
+++ b/artfynd/A 58997-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130222378</v>
       </c>
       <c r="B2" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>130222564</v>
       </c>
       <c r="B3" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>130222885</v>
       </c>
       <c r="B4" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>130222759</v>
       </c>
       <c r="B5" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,42 +1103,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130222398</v>
+        <v>130222889</v>
       </c>
       <c r="B6" t="n">
-        <v>98833</v>
+        <v>93010</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1146,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>557564</v>
+        <v>557475</v>
       </c>
       <c r="R6" t="n">
-        <v>6398402</v>
+        <v>6398291</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,45 +1212,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130222889</v>
+        <v>130222398</v>
       </c>
       <c r="B7" t="n">
-        <v>92923</v>
+        <v>98920</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>557475</v>
+        <v>557564</v>
       </c>
       <c r="R7" t="n">
-        <v>6398291</v>
+        <v>6398402</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1321,7 +1321,7 @@
         <v>130222761</v>
       </c>
       <c r="B8" t="n">
-        <v>91662</v>
+        <v>91749</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>130222371</v>
       </c>
       <c r="B9" t="n">
-        <v>92291</v>
+        <v>92378</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>130222698</v>
       </c>
       <c r="B10" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>130222194</v>
       </c>
       <c r="B11" t="n">
-        <v>92923</v>
+        <v>93010</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>130222391</v>
       </c>
       <c r="B12" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>130222384</v>
       </c>
       <c r="B13" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,10 +1963,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130222404</v>
+        <v>130222693</v>
       </c>
       <c r="B14" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557549</v>
+        <v>557564</v>
       </c>
       <c r="R14" t="n">
-        <v>6398333</v>
+        <v>6398309</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2069,10 +2069,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130222693</v>
+        <v>130222404</v>
       </c>
       <c r="B15" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2112,10 +2112,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>557564</v>
+        <v>557549</v>
       </c>
       <c r="R15" t="n">
-        <v>6398309</v>
+        <v>6398333</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 58997-2025 artfynd.xlsx
+++ b/artfynd/A 58997-2025 artfynd.xlsx
@@ -1963,7 +1963,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130222693</v>
+        <v>130222404</v>
       </c>
       <c r="B14" t="n">
         <v>98920</v>
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557564</v>
+        <v>557549</v>
       </c>
       <c r="R14" t="n">
-        <v>6398309</v>
+        <v>6398333</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2069,7 +2069,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130222404</v>
+        <v>130222693</v>
       </c>
       <c r="B15" t="n">
         <v>98920</v>
@@ -2112,10 +2112,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>557549</v>
+        <v>557564</v>
       </c>
       <c r="R15" t="n">
-        <v>6398333</v>
+        <v>6398309</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 58997-2025 artfynd.xlsx
+++ b/artfynd/A 58997-2025 artfynd.xlsx
@@ -1103,45 +1103,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130222889</v>
+        <v>130222398</v>
       </c>
       <c r="B6" t="n">
-        <v>93010</v>
+        <v>98920</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1149,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>557475</v>
+        <v>557564</v>
       </c>
       <c r="R6" t="n">
-        <v>6398291</v>
+        <v>6398402</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,42 +1209,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130222398</v>
+        <v>130222889</v>
       </c>
       <c r="B7" t="n">
-        <v>98920</v>
+        <v>93010</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>557564</v>
+        <v>557475</v>
       </c>
       <c r="R7" t="n">
-        <v>6398402</v>
+        <v>6398291</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 58997-2025 artfynd.xlsx
+++ b/artfynd/A 58997-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130222378</v>
       </c>
       <c r="B2" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>130222564</v>
       </c>
       <c r="B3" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>130222885</v>
       </c>
       <c r="B4" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>130222759</v>
       </c>
       <c r="B5" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>130222398</v>
       </c>
       <c r="B6" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>130222889</v>
       </c>
       <c r="B7" t="n">
-        <v>93010</v>
+        <v>93013</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>130222761</v>
       </c>
       <c r="B8" t="n">
-        <v>91749</v>
+        <v>91752</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>130222371</v>
       </c>
       <c r="B9" t="n">
-        <v>92378</v>
+        <v>92381</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>130222698</v>
       </c>
       <c r="B10" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>130222194</v>
       </c>
       <c r="B11" t="n">
-        <v>93010</v>
+        <v>93013</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>130222391</v>
       </c>
       <c r="B12" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>130222384</v>
       </c>
       <c r="B13" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>130222404</v>
       </c>
       <c r="B14" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>130222693</v>
       </c>
       <c r="B15" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 58997-2025 artfynd.xlsx
+++ b/artfynd/A 58997-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130222378</v>
       </c>
       <c r="B2" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>130222564</v>
       </c>
       <c r="B3" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>130222885</v>
       </c>
       <c r="B4" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>130222759</v>
       </c>
       <c r="B5" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,42 +1103,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130222398</v>
+        <v>130222889</v>
       </c>
       <c r="B6" t="n">
-        <v>98923</v>
+        <v>93039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1146,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>557564</v>
+        <v>557475</v>
       </c>
       <c r="R6" t="n">
-        <v>6398402</v>
+        <v>6398291</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,45 +1212,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130222889</v>
+        <v>130222398</v>
       </c>
       <c r="B7" t="n">
-        <v>93013</v>
+        <v>98949</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>557475</v>
+        <v>557564</v>
       </c>
       <c r="R7" t="n">
-        <v>6398291</v>
+        <v>6398402</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1321,7 +1321,7 @@
         <v>130222761</v>
       </c>
       <c r="B8" t="n">
-        <v>91752</v>
+        <v>91778</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>130222371</v>
       </c>
       <c r="B9" t="n">
-        <v>92381</v>
+        <v>92407</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>130222698</v>
       </c>
       <c r="B10" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>130222194</v>
       </c>
       <c r="B11" t="n">
-        <v>93013</v>
+        <v>93039</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>130222391</v>
       </c>
       <c r="B12" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>130222384</v>
       </c>
       <c r="B13" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>130222404</v>
       </c>
       <c r="B14" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>130222693</v>
       </c>
       <c r="B15" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 58997-2025 artfynd.xlsx
+++ b/artfynd/A 58997-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130222378</v>
       </c>
       <c r="B2" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>130222564</v>
       </c>
       <c r="B3" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>130222885</v>
       </c>
       <c r="B4" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>130222759</v>
       </c>
       <c r="B5" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>130222889</v>
       </c>
       <c r="B6" t="n">
-        <v>93039</v>
+        <v>93040</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>130222398</v>
       </c>
       <c r="B7" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>130222761</v>
       </c>
       <c r="B8" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>130222371</v>
       </c>
       <c r="B9" t="n">
-        <v>92407</v>
+        <v>92408</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>130222698</v>
       </c>
       <c r="B10" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>130222194</v>
       </c>
       <c r="B11" t="n">
-        <v>93039</v>
+        <v>93040</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>130222391</v>
       </c>
       <c r="B12" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>130222384</v>
       </c>
       <c r="B13" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,10 +1963,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130222404</v>
+        <v>130222693</v>
       </c>
       <c r="B14" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557549</v>
+        <v>557564</v>
       </c>
       <c r="R14" t="n">
-        <v>6398333</v>
+        <v>6398309</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2069,10 +2069,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130222693</v>
+        <v>130222404</v>
       </c>
       <c r="B15" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2112,10 +2112,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>557564</v>
+        <v>557549</v>
       </c>
       <c r="R15" t="n">
-        <v>6398309</v>
+        <v>6398333</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 58997-2025 artfynd.xlsx
+++ b/artfynd/A 58997-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130222378</v>
       </c>
       <c r="B2" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>130222564</v>
       </c>
       <c r="B3" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>130222885</v>
       </c>
       <c r="B4" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>130222759</v>
       </c>
       <c r="B5" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>130222889</v>
       </c>
       <c r="B6" t="n">
-        <v>93040</v>
+        <v>93041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>130222398</v>
       </c>
       <c r="B7" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>130222761</v>
       </c>
       <c r="B8" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>130222371</v>
       </c>
       <c r="B9" t="n">
-        <v>92408</v>
+        <v>92409</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>130222698</v>
       </c>
       <c r="B10" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>130222194</v>
       </c>
       <c r="B11" t="n">
-        <v>93040</v>
+        <v>93041</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>130222391</v>
       </c>
       <c r="B12" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>130222384</v>
       </c>
       <c r="B13" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,10 +1963,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130222693</v>
+        <v>130222404</v>
       </c>
       <c r="B14" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557564</v>
+        <v>557549</v>
       </c>
       <c r="R14" t="n">
-        <v>6398309</v>
+        <v>6398333</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2069,10 +2069,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130222404</v>
+        <v>130222693</v>
       </c>
       <c r="B15" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2112,10 +2112,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>557549</v>
+        <v>557564</v>
       </c>
       <c r="R15" t="n">
-        <v>6398333</v>
+        <v>6398309</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 58997-2025 artfynd.xlsx
+++ b/artfynd/A 58997-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130222378</v>
       </c>
       <c r="B2" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>130222564</v>
       </c>
       <c r="B3" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>130222885</v>
       </c>
       <c r="B4" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>130222759</v>
       </c>
       <c r="B5" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,45 +1103,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130222889</v>
+        <v>130222398</v>
       </c>
       <c r="B6" t="n">
-        <v>93041</v>
+        <v>98953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1149,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>557475</v>
+        <v>557564</v>
       </c>
       <c r="R6" t="n">
-        <v>6398291</v>
+        <v>6398402</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,42 +1209,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130222398</v>
+        <v>130222889</v>
       </c>
       <c r="B7" t="n">
-        <v>98951</v>
+        <v>93043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>557564</v>
+        <v>557475</v>
       </c>
       <c r="R7" t="n">
-        <v>6398402</v>
+        <v>6398291</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1321,7 +1321,7 @@
         <v>130222761</v>
       </c>
       <c r="B8" t="n">
-        <v>91780</v>
+        <v>91782</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>130222371</v>
       </c>
       <c r="B9" t="n">
-        <v>92409</v>
+        <v>92411</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>130222698</v>
       </c>
       <c r="B10" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>130222194</v>
       </c>
       <c r="B11" t="n">
-        <v>93041</v>
+        <v>93043</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>130222391</v>
       </c>
       <c r="B12" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>130222384</v>
       </c>
       <c r="B13" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,10 +1963,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130222404</v>
+        <v>130222693</v>
       </c>
       <c r="B14" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557549</v>
+        <v>557564</v>
       </c>
       <c r="R14" t="n">
-        <v>6398333</v>
+        <v>6398309</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2069,10 +2069,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130222693</v>
+        <v>130222404</v>
       </c>
       <c r="B15" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2112,10 +2112,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>557564</v>
+        <v>557549</v>
       </c>
       <c r="R15" t="n">
-        <v>6398309</v>
+        <v>6398333</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 58997-2025 artfynd.xlsx
+++ b/artfynd/A 58997-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130222378</v>
       </c>
       <c r="B2" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>130222564</v>
       </c>
       <c r="B3" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>130222885</v>
       </c>
       <c r="B4" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>130222759</v>
       </c>
       <c r="B5" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>130222398</v>
       </c>
       <c r="B6" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>130222889</v>
       </c>
       <c r="B7" t="n">
-        <v>93043</v>
+        <v>93047</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>130222371</v>
       </c>
       <c r="B9" t="n">
-        <v>92411</v>
+        <v>92415</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>130222698</v>
       </c>
       <c r="B10" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>130222194</v>
       </c>
       <c r="B11" t="n">
-        <v>93043</v>
+        <v>93047</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,7 +1754,7 @@
         <v>130222391</v>
       </c>
       <c r="B12" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>130222384</v>
       </c>
       <c r="B13" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,10 +1963,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130222693</v>
+        <v>130222404</v>
       </c>
       <c r="B14" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>557564</v>
+        <v>557549</v>
       </c>
       <c r="R14" t="n">
-        <v>6398309</v>
+        <v>6398333</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2069,10 +2069,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130222404</v>
+        <v>130222693</v>
       </c>
       <c r="B15" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2112,10 +2112,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>557549</v>
+        <v>557564</v>
       </c>
       <c r="R15" t="n">
-        <v>6398333</v>
+        <v>6398309</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 58997-2025 artfynd.xlsx
+++ b/artfynd/A 58997-2025 artfynd.xlsx
@@ -1103,42 +1103,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130222398</v>
+        <v>130222889</v>
       </c>
       <c r="B6" t="n">
-        <v>98957</v>
+        <v>93047</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1146,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>557564</v>
+        <v>557475</v>
       </c>
       <c r="R6" t="n">
-        <v>6398402</v>
+        <v>6398291</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,45 +1212,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130222889</v>
+        <v>130222398</v>
       </c>
       <c r="B7" t="n">
-        <v>93047</v>
+        <v>98957</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>557475</v>
+        <v>557564</v>
       </c>
       <c r="R7" t="n">
-        <v>6398291</v>
+        <v>6398402</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
